--- a/Day03/배포용/비전공/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/Day03/배포용/비전공/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\ai-onboarding\Day03\공통\프로젝트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edwin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E46F63A-ABA1-45C5-984C-C2E6F9904D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C6CE59-3E60-447C-A3B3-EE8079CB4F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="23160" windowHeight="16500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -22,19 +22,6 @@
     <sheet name="6_용어설명(참고)" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -197,9 +184,6 @@
     <t>Won't have (이번 MVP 범위에서 제외 - 스코프 크립: 범위가 계속 늘어나는 현상 방지)</t>
   </si>
   <si>
-    <t>리스크 및 대응 (실습: 프롬프트가이드 탭의 '리스크점검' 프롬프트 활용)</t>
-  </si>
-  <si>
     <t>LocalHub WBS + 간트차트 (Day 1~Day 3 기준)</t>
   </si>
   <si>
@@ -5254,13 +5238,849 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>위에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확정한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MVP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바탕으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> WBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성해줘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> YYYY-MM-DD(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">납기는
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>YYYY-MM-DD(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납기로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대분류는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기획</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문서화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발표준비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나누고
+각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작업마다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작업명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담당자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(FE/BE/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팀전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시작일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종료일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선행작업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만들어줘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>요구사항분석</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>②</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>아이디어도출</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>④</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> WBS(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작업분해구조</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 프로젝트의 MVP 범위를 MoSCoW 방식으로 정리해줘._x000B_Must have는 개발 의뢰 문서(RFP)의 '필수' 항목 그대로, Should/Could have는 평가 결과를 고려,Won't have(이번엔 안 하는 것)도 명확히 구분해서 표로 만들어줘.--- (개발 의뢰 문서(RFP) 원문 전체 및 평가 결과 넣기) ---</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>우리</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5279,7 +6099,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5298,7 +6118,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 3</t>
@@ -5317,7 +6137,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -5336,7 +6156,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> VSCode Copilot + OpenAI API</t>
@@ -5355,7 +6175,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5374,7 +6194,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -5393,7 +6213,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5412,7 +6232,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5431,7 +6251,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5450,7 +6270,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">.
@@ -5470,7 +6290,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5489,7 +6309,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5508,7 +6328,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> N</t>
@@ -5527,7 +6347,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5546,7 +6366,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5565,7 +6385,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5584,7 +6404,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5603,7 +6423,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5622,7 +6442,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5641,7 +6461,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5660,7 +6480,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5679,7 +6499,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">:
@@ -5699,7 +6519,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5718,7 +6538,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> [</t>
@@ -5737,7 +6557,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 1~5, </t>
@@ -5750,13 +6570,183 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>실현가능성(난이도가 낮을수록 높음)과 임팩트(사용자 체감 효과)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+      <t>실현가능성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난이도가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낮을수록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>효과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t>]</t>
@@ -5775,7 +6765,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5794,7 +6784,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5813,7 +6803,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
-        <rFont val="Arial"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t>.</t>
@@ -5827,839 +6817,102 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">
---- (선택 가능한 후보 표 붙여넣기, 9 page 내용 ) ---</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 프로젝트의 MVP 범위를 MoSCoW 방식으로 정리해줘._x000B_Must have는 개발 의뢰 문서(RFP)의 '필수' 항목 그대로, _x000B_Should/Could have는 평과 결과를 고려,Won't have(이번엔 안 하는 것)도 명확히 구분해서 표로 만들어줘._x000B_--- (개발 의뢰 문서(RFP) 원문 전체 및 평가 결과 넣기) ---</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확정한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MVP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>범위를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바탕으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> WBS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성해줘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> YYYY-MM-DD(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">납기는
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>YYYY-MM-DD(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>납기로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>) 15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대분류는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기획</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배포</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>문서화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>발표준비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나누고
-각</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업마다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>담당자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(FE/BE/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팀전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시작일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>종료일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선행작업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>만들어줘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+--- (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능한</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>요구사항분석</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>②</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>아이디어도출</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="1"/>
-      </rPr>
-      <t>④</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> WBS(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업분해구조</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붙여넣기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>) ---</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -6671,7 +6924,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6951,6 +7204,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -7123,7 +7383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7134,7 +7394,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -7160,9 +7419,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7190,12 +7446,46 @@
     <xf numFmtId="0" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7219,19 +7509,31 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7294,39 +7596,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7620,25 +7889,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="34"/>
+    </row>
+    <row r="4" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B4" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="28"/>
-    </row>
-    <row r="4" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B4" s="18" t="s">
+      <c r="C4" s="15" t="s">
         <v>112</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.950000000000003" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>114</v>
+      <c r="C5" s="15" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="19.5" customHeight="1">
@@ -7646,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="19.5" customHeight="1">
@@ -7654,86 +7923,86 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1">
+      <c r="B9" s="30" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="26" t="s">
+      <c r="C9" s="31"/>
+    </row>
+    <row r="10" spans="2:3" ht="27">
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="27"/>
-    </row>
-    <row r="10" spans="2:3" ht="40.5">
-      <c r="B10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="19" t="s">
+    </row>
+    <row r="11" spans="2:3" ht="40.5">
+      <c r="B11" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="40.5">
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="19" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="33.75" customHeight="1">
+      <c r="B12" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="2:3" ht="33.75" customHeight="1">
+      <c r="B13" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="33.75" customHeight="1">
+      <c r="B14" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="2:3" ht="33.75" customHeight="1">
+      <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="19" t="s">
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="33"/>
+    </row>
+    <row r="18" spans="2:3" ht="27.75" customHeight="1">
+      <c r="B18" s="35" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="69"/>
-    </row>
-    <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="65"/>
+      <c r="C18" s="36"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="67"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="67"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -7756,160 +8025,163 @@
   <sheetPr>
     <tabColor rgb="FF1E2761"/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="B2:J13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="74.42578125" customWidth="1"/>
     <col min="5" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="31" t="s">
+    <row r="2" spans="2:10" ht="30" customHeight="1">
+      <c r="B2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-    </row>
-    <row r="4" spans="2:6" ht="19.5" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
+    <row r="4" spans="2:10" ht="19.5" customHeight="1">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B5" s="71" t="s">
+    <row r="5" spans="2:10" ht="129.75" customHeight="1">
+      <c r="B5" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="129.75" customHeight="1">
+      <c r="B6" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="129.75" customHeight="1">
+      <c r="B7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="73" t="s">
+      <c r="E7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="129.75" customHeight="1">
+      <c r="B8" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F5" s="72" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B6" s="71" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="72" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B7" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B8" s="74" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="14.1" customHeight="1"/>
-    <row r="10" spans="2:6" ht="15" customHeight="1">
-      <c r="B10" s="33" t="s">
+    <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
+    <row r="10" spans="2:10" ht="15" customHeight="1">
+      <c r="B10" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" spans="2:10" ht="24" customHeight="1">
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="27"/>
-    </row>
-    <row r="11" spans="2:6" ht="24" customHeight="1">
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+    </row>
+    <row r="12" spans="2:10" ht="24" customHeight="1">
+      <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C12" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" spans="2:6" ht="24" customHeight="1">
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+    </row>
+    <row r="13" spans="2:10" ht="24" customHeight="1">
+      <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C13" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-    </row>
-    <row r="13" spans="2:6" ht="24" customHeight="1">
-      <c r="B13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7934,48 +8206,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="27"/>
+      <c r="B3" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="31"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15" customHeight="1">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
       <c r="B6" s="3"/>
@@ -8137,167 +8409,167 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="31"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="27"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="31"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="13"/>
+      <c r="B6" s="12"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="str">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="str">
         <f t="shared" ref="G6:G13" si="0">IF(OR(E6="",F6=""),"",E6*F6*2)</f>
         <v/>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B7" s="13"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="str">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B8" s="13"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="str">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B9" s="13"/>
+      <c r="B9" s="12"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="str">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B10" s="13"/>
+      <c r="B10" s="12"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="str">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B11" s="13"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="str">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B12" s="13"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="str">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="13"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6" t="str">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="15" spans="2:8" ht="118.7" customHeight="1">
-      <c r="B15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8332,26 +8604,26 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:C29"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="3" max="3" width="88.5703125" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="40"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -8378,103 +8650,85 @@
       <c r="C7" s="2"/>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="54"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="41"/>
-      <c r="C10" s="42"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="41"/>
-      <c r="C12" s="42"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="52"/>
     </row>
     <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="41"/>
-      <c r="C17" s="42"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
     </row>
     <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="41"/>
-      <c r="C19" s="42"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="16"/>
+      <c r="C21" s="50"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="41"/>
-      <c r="C22" s="42"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
-    </row>
-    <row r="26" spans="2:3" ht="15" customHeight="1">
-      <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
-    </row>
-    <row r="28" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B28" s="41"/>
-      <c r="C28" s="42"/>
-    </row>
-    <row r="29" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8504,394 +8758,394 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+    </row>
+    <row r="3" spans="2:13" ht="79.7" customHeight="1">
+      <c r="B3" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="31"/>
+    </row>
+    <row r="4" spans="2:13" ht="25.5" customHeight="1">
+      <c r="B4" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="27"/>
-    </row>
-    <row r="4" spans="2:13" ht="25.5" customHeight="1">
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="H4" s="22" t="s">
+      <c r="I4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="23">
+      <c r="K4" s="19">
         <v>1</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="19">
         <v>2</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="30" customHeight="1">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="str">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="str">
         <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
         <v/>
       </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" ht="30" customHeight="1">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6" t="str">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" ht="30" customHeight="1">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="str">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="2:13" ht="30" customHeight="1">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="str">
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="2:13" ht="30" customHeight="1">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6" t="str">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="2:13" ht="30" customHeight="1">
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="str">
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="str">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6" t="str">
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="str">
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:13" ht="30" customHeight="1">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="str">
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6" t="str">
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6" t="str">
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" spans="2:13" ht="30" customHeight="1">
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>13</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6" t="str">
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="2:13" ht="30" customHeight="1">
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>14</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6" t="str">
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="59"/>
+      <c r="B20" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="71"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="73"/>
+    </row>
+    <row r="22" spans="2:13" ht="15" customHeight="1">
+      <c r="B22" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="61"/>
-    </row>
-    <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="62" t="s">
+      <c r="C22" s="75"/>
+    </row>
+    <row r="23" spans="2:13" ht="15" customHeight="1">
+      <c r="B23" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="63"/>
-    </row>
-    <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="46" t="s">
+      <c r="C23" s="59"/>
+    </row>
+    <row r="24" spans="2:13" ht="15" customHeight="1">
+      <c r="B24" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="47"/>
-    </row>
-    <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="48" t="s">
+      <c r="C24" s="61"/>
+    </row>
+    <row r="25" spans="2:13" ht="15" customHeight="1">
+      <c r="B25" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="49"/>
-    </row>
-    <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="50" t="s">
+      <c r="C25" s="63"/>
+    </row>
+    <row r="26" spans="2:13" ht="15" customHeight="1">
+      <c r="B26" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="51"/>
-    </row>
-    <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="52" t="s">
+      <c r="C26" s="65"/>
+    </row>
+    <row r="27" spans="2:13" ht="15" customHeight="1">
+      <c r="B27" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="53"/>
-    </row>
-    <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="54" t="s">
+      <c r="C27" s="67"/>
+    </row>
+    <row r="28" spans="2:13" ht="15" customHeight="1">
+      <c r="B28" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="55"/>
-    </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="45"/>
+      <c r="C28" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -8942,183 +9196,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="40"/>
+    </row>
+    <row r="3" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B3" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="32"/>
-    </row>
-    <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="37" t="s">
+      <c r="C3" s="31"/>
+    </row>
+    <row r="5" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="27"/>
-    </row>
-    <row r="5" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="6" spans="2:3" ht="30" customHeight="1">
+      <c r="B6" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1">
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="30" customHeight="1">
+      <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="30" customHeight="1">
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="30" customHeight="1">
+      <c r="B8" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="30" customHeight="1">
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1">
       <c r="B9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="2:3" ht="30" customHeight="1">
+      <c r="B10" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" ht="30" customHeight="1">
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" spans="2:3" ht="30" customHeight="1">
+      <c r="B11" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="30" customHeight="1">
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="30" customHeight="1">
+      <c r="B12" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="30" customHeight="1">
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="30" customHeight="1">
       <c r="B13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="30" customHeight="1">
+      <c r="B14" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" ht="30" customHeight="1">
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30" customHeight="1">
       <c r="B15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="30" customHeight="1">
       <c r="B16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="17" spans="2:3" ht="30" customHeight="1">
+      <c r="B17" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1">
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1">
       <c r="B18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1">
       <c r="B19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30" customHeight="1">
       <c r="B20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1">
       <c r="B21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="30" customHeight="1">
       <c r="B22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="23" spans="2:3" ht="30" customHeight="1">
+      <c r="B23" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1">
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="24" spans="2:3" ht="30" customHeight="1">
+      <c r="B24" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1">
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="25" spans="2:3" ht="30" customHeight="1">
+      <c r="B25" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1">
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
